--- a/sheets/조재수대금교본/검수/구 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/구 아리랑.xlsx
@@ -3974,8 +3974,7 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–
-ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -4003,8 +4002,7 @@
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–
-ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -4014,7 +4012,7 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -4027,7 +4025,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㄴ
+          <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
@@ -4050,11 +4048,7 @@
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
@@ -4073,52 +4067,37 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-ﾉ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21"/>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太∽</t>
+–太</t>
         </is>
       </c>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="O5" s="24"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
@@ -4127,16 +4106,11 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ
-∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧∽</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -4146,21 +4120,20 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧林南
-ﾉ
-–太∽</t>
+          <t xml:space="preserve">林南
+–太</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -4172,15 +4145,14 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧林南
-ﾉ
-–太∽</t>
+          <t xml:space="preserve">林南
+–太</t>
         </is>
       </c>
       <c r="S6" s="22"/>
@@ -4201,7 +4173,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -4214,21 +4186,21 @@
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汏
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4250,59 +4222,43 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
     <row r="9" ht="119.22" customHeight="true">
@@ -4312,7 +4268,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汏ㄴ</t>
+汏</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4369,56 +4325,56 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-淋∽</t>
+淋</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-–⌝</t>
+          <t xml:space="preserve">汰
+–</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-–⌝</t>
+          <t xml:space="preserve">汰
+–</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -4427,31 +4383,27 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="24"/>
       <c r="F11" s="21"/>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧汏㳞
-–⌝</t>
+          <t xml:space="preserve">汏㳞
+–</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>
@@ -4465,15 +4417,15 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 南</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧汰㳞
-–⌝</t>
+          <t xml:space="preserve">汰㳞
+–</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -4484,7 +4436,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4496,8 +4448,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ
-∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -4509,8 +4460,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ
-∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4522,8 +4472,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ
-∽</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4541,7 +4490,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4552,7 +4501,7 @@
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -4560,8 +4509,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -4570,7 +4518,7 @@
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="S13" s="23"/>
@@ -4582,16 +4530,11 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -4603,8 +4546,7 @@
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–∼
-‹</t>
+–∼</t>
         </is>
       </c>
       <c r="K14" s="24"/>
@@ -4618,8 +4560,7 @@
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-–∼
-‹</t>
+–∼</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/구 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/구 아리랑.xlsx
@@ -3974,7 +3974,8 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–</t>
+–
+ﾉ</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -4002,7 +4003,8 @@
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–</t>
+–
+ﾉ</t>
         </is>
       </c>
       <c r="S3" s="22"/>
@@ -4012,7 +4014,7 @@
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -4025,7 +4027,7 @@
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ㄴ
 潢</t>
         </is>
       </c>
@@ -4048,7 +4050,11 @@
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
@@ -4067,7 +4073,8 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+ﾉ</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -4084,7 +4091,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–太</t>
+–太∽</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -4106,11 +4113,16 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅋ
+∽</t>
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧∽</t>
+        </is>
+      </c>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -4120,20 +4132,21 @@
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
-–太</t>
+          <t xml:space="preserve">∧林南
+ﾉ
+–太∽</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -4145,14 +4158,15 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="Q6" s="22"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林南
-–太</t>
+          <t xml:space="preserve">∧林南
+ﾉ
+–太∽</t>
         </is>
       </c>
       <c r="S6" s="22"/>
@@ -4173,7 +4187,7 @@
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="I7" s="23"/>
@@ -4186,21 +4200,21 @@
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汏
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4247,7 +4261,7 @@
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="O8" s="24"/>
@@ -4268,7 +4282,7 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汏</t>
+汏ㄴ</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4325,56 +4339,56 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-淋</t>
+淋∽</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-–</t>
+          <t xml:space="preserve">汰∧
+–⌝</t>
         </is>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-–</t>
+          <t xml:space="preserve">汰∧
+–⌝</t>
         </is>
       </c>
       <c r="S10" s="23"/>
@@ -4389,21 +4403,21 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 南</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汏㳞
-–</t>
+          <t xml:space="preserve">∧汏㳞
+–⌝</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 南</t>
         </is>
       </c>
@@ -4417,15 +4431,15 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 南</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
-–</t>
+          <t xml:space="preserve">∧汰㳞
+–⌝</t>
         </is>
       </c>
       <c r="S11" s="24"/>
@@ -4436,7 +4450,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4448,7 +4462,8 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅋ
+∽</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -4460,7 +4475,8 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅋ
+∽</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4472,7 +4488,8 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅋ
+∽</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -4490,7 +4507,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4501,7 +4518,7 @@
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -4509,7 +4526,8 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -4518,7 +4536,7 @@
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="S13" s="23"/>

--- a/sheets/조재수대금교본/검수/구 아리랑.xlsx
+++ b/sheets/조재수대금교본/검수/구 아리랑.xlsx
@@ -3894,30 +3894,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="80.0" customHeight="true">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="119.22" customHeight="true">
+    <row r="3" ht="124.21" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="119.22" customHeight="true">
+    <row r="4" ht="124.21" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="119.22" customHeight="true">
+    <row r="5" ht="124.21" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="119.22" customHeight="true">
+    <row r="6" ht="124.21" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="119.22" customHeight="true">
+    <row r="7" ht="124.21" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="119.22" customHeight="true">
+    <row r="8" ht="124.21" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="119.22" customHeight="true">
+    <row r="9" ht="124.21" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="119.22" customHeight="true">
+    <row r="10" ht="124.21" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="119.22" customHeight="true">
+    <row r="11" ht="124.21" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="119.22" customHeight="true">
+    <row r="12" ht="124.21" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="119.22" customHeight="true">
+    <row r="13" ht="124.21" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="119.22" customHeight="true">
+    <row r="14" ht="124.21" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4603,6 +4603,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>